--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T10:14:31+00:00</t>
+    <t>2026-07-08T15:46:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T15:46:54+00:00</t>
+    <t>2026-07-09T09:13:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:13:13+00:00</t>
+    <t>2026-07-10T12:01:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:01:50+00:00</t>
+    <t>2026-07-10T12:28:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:28:44+00:00</t>
+    <t>2026-07-10T12:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:58:40+00:00</t>
+    <t>2026-07-20T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:08:41+00:00</t>
+    <t>2026-07-21T09:08:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -8700,7 +8700,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>92</v>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2292" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2293" uniqueCount="405">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:08:11+00:00</t>
+    <t>2026-07-21T09:10:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -799,7 +799,7 @@
     <t>Condition.severity</t>
   </si>
   <si>
-    <t>Sévérité</t>
+    <t>Subjective severity of condition</t>
   </si>
   <si>
     <t>A subjective assessment of the severity of the condition as evaluated by the clinician.</t>
@@ -808,7 +808,7 @@
     <t>Coding of the severity with a terminology is preferred, where possible.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-severite-observation-cisis|20260619134042</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-severity|4.0.1</t>
   </si>
   <si>
     <t>&lt; 272141005 |Severities|</t>
@@ -5771,9 +5771,11 @@
         <v>79</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="Z35" t="s" s="2">
         <v>254</v>
       </c>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:10:59+00:00</t>
+    <t>2026-07-22T09:27:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:27:19+00:00</t>
+    <t>2026-07-28T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T07:28:06+00:00</t>
+    <t>2026-07-30T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T08:11:50+00:00</t>
+    <t>2026-08-03T07:00:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T07:00:21+00:00</t>
+    <t>2026-08-04T07:50:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T07:50:37+00:00</t>
+    <t>2026-08-04T08:17:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:17:33+00:00</t>
+    <t>2026-08-06T12:56:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T12:56:12+00:00</t>
+    <t>2026-08-07T08:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:15:28+00:00</t>
+    <t>2026-08-07T09:41:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:41:31+00:00</t>
+    <t>2026-08-07T12:53:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T12:53:43+00:00</t>
+    <t>2026-09-03T14:46:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -781,7 +781,7 @@
     <t>The categorization is often highly contextual and may appear poorly differentiated or not very useful in other contexts.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-code-probleme-cisis|20260619134043</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-code-probleme-cisis|20260716085853</t>
   </si>
   <si>
     <t>&lt; 404684003 |Clinical finding|</t>
@@ -1157,7 +1157,7 @@
     <t>A simple summary of the stage such as "Stage 3". The determination of the stage is disease-specific.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-health-status-code-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-health-status-code-cisis|20260716085852</t>
   </si>
   <si>
     <t xml:space="preserve">con-1
@@ -6424,7 +6424,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>312</v>
       </c>
@@ -6445,7 +6445,7 @@
         <v>91</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>79</v>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T14:46:57+00:00</t>
+    <t>2026-09-04T09:26:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:26:41+00:00</t>
+    <t>2026-09-04T11:53:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
